--- a/ProjectManagement/Checklist.xlsx
+++ b/ProjectManagement/Checklist.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBEDBD8-D37D-4A48-9B82-881FE7040B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="165" windowWidth="14805" windowHeight="7950"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
@@ -15,7 +16,20 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -436,7 +450,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1180,17 +1194,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
@@ -1198,8 +1208,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1235,7 +1255,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 26" descr="10%"/>
+        <xdr:cNvPr id="2" name="Rectangle 26" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1283,7 +1309,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Text Box 11"/>
+        <xdr:cNvPr id="3" name="Text Box 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1333,7 +1365,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Text Box 12"/>
+        <xdr:cNvPr id="4" name="Text Box 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1404,7 +1442,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Line 1"/>
+        <xdr:cNvPr id="5" name="Line 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeShapeType="1"/>
         </xdr:cNvSpPr>
@@ -1452,7 +1496,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Line 2"/>
+        <xdr:cNvPr id="6" name="Line 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeShapeType="1"/>
         </xdr:cNvSpPr>
@@ -1500,7 +1550,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="AutoShape 3"/>
+        <xdr:cNvPr id="7" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1545,7 +1601,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="AutoShape 4"/>
+        <xdr:cNvPr id="8" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1590,7 +1652,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="AutoShape 5"/>
+        <xdr:cNvPr id="9" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1635,7 +1703,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="AutoShape 6"/>
+        <xdr:cNvPr id="10" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1680,7 +1754,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="AutoShape 7"/>
+        <xdr:cNvPr id="11" name="AutoShape 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1725,7 +1805,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Text Box 9"/>
+        <xdr:cNvPr id="12" name="Text Box 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1775,7 +1861,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Text Box 10"/>
+        <xdr:cNvPr id="13" name="Text Box 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1825,7 +1917,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="Text Box 13"/>
+        <xdr:cNvPr id="14" name="Text Box 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1896,7 +1994,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%"/>
+        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1944,7 +2048,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="Rectangle 15" descr="10%"/>
+        <xdr:cNvPr id="16" name="Rectangle 15" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -1992,22 +2102,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="17" name="Group 21"/>
+        <xdr:cNvPr id="17" name="Group 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8115300" y="5038725"/>
-          <a:ext cx="1838325" cy="190500"/>
+          <a:off x="8750300" y="5067300"/>
+          <a:ext cx="2028825" cy="190500"/>
           <a:chOff x="691" y="481"/>
           <a:chExt cx="144" cy="27"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="Rectangle 16" descr="10%"/>
+          <xdr:cNvPr id="18" name="Rectangle 16" descr="10%">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks noChangeArrowheads="1"/>
           </xdr:cNvSpPr>
@@ -2040,7 +2162,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="Rectangle 17" descr="10%"/>
+          <xdr:cNvPr id="19" name="Rectangle 17" descr="10%">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks noChangeArrowheads="1"/>
           </xdr:cNvSpPr>
@@ -2073,7 +2201,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="Freeform 19"/>
+          <xdr:cNvPr id="20" name="Freeform 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks/>
           </xdr:cNvSpPr>
@@ -2150,7 +2284,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="Freeform 20"/>
+          <xdr:cNvPr id="21" name="Freeform 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks/>
           </xdr:cNvSpPr>
@@ -2243,7 +2383,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="Rectangle 22"/>
+        <xdr:cNvPr id="22" name="Rectangle 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2286,7 +2432,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="Text Box 23"/>
+        <xdr:cNvPr id="23" name="Text Box 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2382,7 +2534,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="Text Box 24"/>
+        <xdr:cNvPr id="24" name="Text Box 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2446,7 +2604,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="AutoShape 27"/>
+        <xdr:cNvPr id="25" name="AutoShape 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2513,7 +2677,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="AutoShape 28"/>
+        <xdr:cNvPr id="26" name="AutoShape 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2595,7 +2765,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="AutoShape 29"/>
+        <xdr:cNvPr id="27" name="AutoShape 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2677,7 +2853,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="AutoShape 30"/>
+        <xdr:cNvPr id="28" name="AutoShape 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2744,7 +2926,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="AutoShape 31"/>
+        <xdr:cNvPr id="29" name="AutoShape 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2811,7 +2999,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="AutoShape 32"/>
+        <xdr:cNvPr id="30" name="AutoShape 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2878,7 +3072,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="AutoShape 33"/>
+        <xdr:cNvPr id="31" name="AutoShape 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2960,7 +3160,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="AutoShape 34"/>
+        <xdr:cNvPr id="32" name="AutoShape 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3042,7 +3248,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="AutoShape 35"/>
+        <xdr:cNvPr id="33" name="AutoShape 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3109,7 +3321,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="AutoShape 36"/>
+        <xdr:cNvPr id="34" name="AutoShape 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3201,7 +3419,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="AutoShape 37"/>
+        <xdr:cNvPr id="35" name="AutoShape 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3268,7 +3492,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="AutoShape 38"/>
+        <xdr:cNvPr id="36" name="AutoShape 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3313,7 +3543,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="AutoShape 39"/>
+        <xdr:cNvPr id="37" name="AutoShape 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3380,7 +3616,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="AutoShape 40"/>
+        <xdr:cNvPr id="38" name="AutoShape 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3447,7 +3689,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="AutoShape 41"/>
+        <xdr:cNvPr id="39" name="AutoShape 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3539,7 +3787,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="AutoShape 42"/>
+        <xdr:cNvPr id="40" name="AutoShape 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3606,7 +3860,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="Text Box 44"/>
+        <xdr:cNvPr id="41" name="Text Box 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3702,7 +3962,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="AutoShape 45"/>
+        <xdr:cNvPr id="42" name="AutoShape 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3784,7 +4050,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="AutoShape 46"/>
+        <xdr:cNvPr id="43" name="AutoShape 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3851,7 +4123,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="AutoShape 47"/>
+        <xdr:cNvPr id="44" name="AutoShape 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3918,7 +4196,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="AutoShape 48"/>
+        <xdr:cNvPr id="45" name="AutoShape 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -3985,7 +4269,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="AutoShape 49"/>
+        <xdr:cNvPr id="46" name="AutoShape 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4052,7 +4342,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="AutoShape 50"/>
+        <xdr:cNvPr id="47" name="AutoShape 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4119,7 +4415,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="AutoShape 51"/>
+        <xdr:cNvPr id="48" name="AutoShape 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4186,7 +4488,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="AutoShape 52"/>
+        <xdr:cNvPr id="49" name="AutoShape 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4253,7 +4561,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="AutoShape 53"/>
+        <xdr:cNvPr id="50" name="AutoShape 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4320,7 +4634,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="AutoShape 54"/>
+        <xdr:cNvPr id="51" name="AutoShape 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4387,7 +4707,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="AutoShape 55"/>
+        <xdr:cNvPr id="52" name="AutoShape 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4454,7 +4780,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="53" name="AutoShape 56"/>
+        <xdr:cNvPr id="53" name="AutoShape 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4521,7 +4853,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="AutoShape 57"/>
+        <xdr:cNvPr id="54" name="AutoShape 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4588,7 +4926,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="AutoShape 58"/>
+        <xdr:cNvPr id="55" name="AutoShape 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4655,7 +4999,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="AutoShape 59"/>
+        <xdr:cNvPr id="56" name="AutoShape 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4727,7 +5077,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle 1" descr="10%"/>
+        <xdr:cNvPr id="2" name="Rectangle 1" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4775,7 +5131,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Text Box 2"/>
+        <xdr:cNvPr id="3" name="Text Box 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4825,7 +5187,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Text Box 3"/>
+        <xdr:cNvPr id="4" name="Text Box 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -4896,7 +5264,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Line 4"/>
+        <xdr:cNvPr id="5" name="Line 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeShapeType="1"/>
         </xdr:cNvSpPr>
@@ -4944,7 +5318,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Line 5"/>
+        <xdr:cNvPr id="6" name="Line 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeShapeType="1"/>
         </xdr:cNvSpPr>
@@ -4992,7 +5372,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="AutoShape 6"/>
+        <xdr:cNvPr id="7" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5037,7 +5423,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="AutoShape 7"/>
+        <xdr:cNvPr id="8" name="AutoShape 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5082,7 +5474,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="AutoShape 8"/>
+        <xdr:cNvPr id="9" name="AutoShape 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5127,7 +5525,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="AutoShape 9"/>
+        <xdr:cNvPr id="10" name="AutoShape 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5172,7 +5576,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="AutoShape 10"/>
+        <xdr:cNvPr id="11" name="AutoShape 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5217,7 +5627,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Text Box 11"/>
+        <xdr:cNvPr id="12" name="Text Box 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5267,7 +5683,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Text Box 12"/>
+        <xdr:cNvPr id="13" name="Text Box 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5317,7 +5739,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="Text Box 13"/>
+        <xdr:cNvPr id="14" name="Text Box 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5388,7 +5816,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%"/>
+        <xdr:cNvPr id="15" name="Rectangle 14" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5436,7 +5870,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="Rectangle 15" descr="10%"/>
+        <xdr:cNvPr id="16" name="Rectangle 15" descr="10%">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5484,22 +5924,34 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="17" name="Group 16"/>
+        <xdr:cNvPr id="17" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr>
           <a:grpSpLocks/>
         </xdr:cNvGrpSpPr>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8115300" y="5038725"/>
-          <a:ext cx="1838325" cy="190500"/>
+          <a:off x="8750300" y="5067300"/>
+          <a:ext cx="2028825" cy="190500"/>
           <a:chOff x="691" y="481"/>
           <a:chExt cx="144" cy="27"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="Rectangle 17" descr="10%"/>
+          <xdr:cNvPr id="18" name="Rectangle 17" descr="10%">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000012000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks noChangeArrowheads="1"/>
           </xdr:cNvSpPr>
@@ -5532,7 +5984,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="Rectangle 18" descr="10%"/>
+          <xdr:cNvPr id="19" name="Rectangle 18" descr="10%">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000013000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks noChangeArrowheads="1"/>
           </xdr:cNvSpPr>
@@ -5565,7 +6023,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="20" name="Freeform 19"/>
+          <xdr:cNvPr id="20" name="Freeform 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000014000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks/>
           </xdr:cNvSpPr>
@@ -5642,7 +6106,13 @@
       </xdr:sp>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="21" name="Freeform 20"/>
+          <xdr:cNvPr id="21" name="Freeform 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000015000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr>
             <a:spLocks/>
           </xdr:cNvSpPr>
@@ -5735,7 +6205,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="Rectangle 21"/>
+        <xdr:cNvPr id="22" name="Rectangle 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5778,7 +6254,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="Text Box 22"/>
+        <xdr:cNvPr id="23" name="Text Box 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5874,7 +6356,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="Text Box 23"/>
+        <xdr:cNvPr id="24" name="Text Box 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -5938,7 +6426,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="AutoShape 24"/>
+        <xdr:cNvPr id="25" name="AutoShape 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6005,7 +6499,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="AutoShape 25"/>
+        <xdr:cNvPr id="26" name="AutoShape 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6087,7 +6587,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="AutoShape 26"/>
+        <xdr:cNvPr id="27" name="AutoShape 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6169,7 +6675,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="AutoShape 27"/>
+        <xdr:cNvPr id="28" name="AutoShape 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6236,7 +6748,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="AutoShape 28"/>
+        <xdr:cNvPr id="29" name="AutoShape 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6303,7 +6821,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="AutoShape 29"/>
+        <xdr:cNvPr id="30" name="AutoShape 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6370,7 +6894,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="AutoShape 30"/>
+        <xdr:cNvPr id="31" name="AutoShape 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6452,7 +6982,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="AutoShape 31"/>
+        <xdr:cNvPr id="32" name="AutoShape 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6519,7 +7055,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="AutoShape 32"/>
+        <xdr:cNvPr id="33" name="AutoShape 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6586,7 +7128,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="AutoShape 33"/>
+        <xdr:cNvPr id="34" name="AutoShape 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6668,7 +7216,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="AutoShape 34"/>
+        <xdr:cNvPr id="35" name="AutoShape 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6750,7 +7304,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="AutoShape 35"/>
+        <xdr:cNvPr id="36" name="AutoShape 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6795,7 +7355,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="AutoShape 36"/>
+        <xdr:cNvPr id="37" name="AutoShape 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6862,7 +7428,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="AutoShape 37"/>
+        <xdr:cNvPr id="38" name="AutoShape 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -6929,7 +7501,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="AutoShape 38"/>
+        <xdr:cNvPr id="39" name="AutoShape 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7026,7 +7604,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="AutoShape 39"/>
+        <xdr:cNvPr id="40" name="AutoShape 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7093,7 +7677,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="Text Box 40"/>
+        <xdr:cNvPr id="41" name="Text Box 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1">
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7189,7 +7779,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="AutoShape 41"/>
+        <xdr:cNvPr id="42" name="AutoShape 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7256,7 +7852,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="AutoShape 42"/>
+        <xdr:cNvPr id="43" name="AutoShape 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7323,7 +7925,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="AutoShape 43"/>
+        <xdr:cNvPr id="44" name="AutoShape 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7390,7 +7998,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="Rectangle 44"/>
+        <xdr:cNvPr id="45" name="Rectangle 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7433,7 +8047,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="AutoShape 45"/>
+        <xdr:cNvPr id="46" name="AutoShape 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7500,7 +8120,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="AutoShape 46"/>
+        <xdr:cNvPr id="47" name="AutoShape 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7567,7 +8193,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="AutoShape 47"/>
+        <xdr:cNvPr id="48" name="AutoShape 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7634,7 +8266,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="AutoShape 48"/>
+        <xdr:cNvPr id="49" name="AutoShape 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7701,7 +8339,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="AutoShape 49"/>
+        <xdr:cNvPr id="50" name="AutoShape 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7768,7 +8412,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="AutoShape 50"/>
+        <xdr:cNvPr id="51" name="AutoShape 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7835,7 +8485,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="AutoShape 51"/>
+        <xdr:cNvPr id="52" name="AutoShape 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7902,7 +8558,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="53" name="AutoShape 52"/>
+        <xdr:cNvPr id="53" name="AutoShape 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -7969,7 +8631,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="AutoShape 53"/>
+        <xdr:cNvPr id="54" name="AutoShape 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8036,7 +8704,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="AutoShape 54"/>
+        <xdr:cNvPr id="55" name="AutoShape 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8103,7 +8777,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="AutoShape 55"/>
+        <xdr:cNvPr id="56" name="AutoShape 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8170,7 +8850,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="57" name="AutoShape 56"/>
+        <xdr:cNvPr id="57" name="AutoShape 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8237,7 +8923,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="58" name="AutoShape 57"/>
+        <xdr:cNvPr id="58" name="AutoShape 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -8403,7 +9095,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Report"/>
@@ -8425,10 +9117,27 @@
 </externalLink>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8466,9 +9175,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8503,7 +9212,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8538,7 +9247,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8711,20 +9420,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I79"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -8735,7 +9444,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
@@ -8747,7 +9456,7 @@
       </c>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
       <c r="H6" s="8" t="s">
@@ -8755,19 +9464,19 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B9" s="62" t="s">
+    <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="B9" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="21" x14ac:dyDescent="0.25">
       <c r="A13" s="61" t="s">
         <v>1</v>
       </c>
@@ -8781,126 +9490,159 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A14" s="62" t="s">
+    <row r="14" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A14" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="65" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D15" s="70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" ref="A16:A78" si="0">A15+1</f>
         <v>2</v>
       </c>
-      <c r="B16" s="64" t="s">
+      <c r="B16" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="70"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="65"/>
+      <c r="D16" s="70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B17" s="64" t="s">
+      <c r="B17" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="70"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="65"/>
+      <c r="D17" s="70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B18" s="64" t="s">
+      <c r="B18" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="70"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="65"/>
+      <c r="D18" s="70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B19" s="64" t="s">
+      <c r="B19" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="70"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="65"/>
+      <c r="D19" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B20" s="64" t="s">
+      <c r="B20" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="70"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="65"/>
+      <c r="D20" s="70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B21" s="64" t="s">
+      <c r="B21" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="70"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="65"/>
+      <c r="D21" s="70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B22" s="64" t="s">
+      <c r="B22" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="70"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="65"/>
+      <c r="D22" s="70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="70"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="65"/>
+      <c r="D23" s="70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B24" s="64" t="s">
+      <c r="B24" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="70"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="65"/>
+      <c r="D24" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B25" s="64" t="s">
+      <c r="B25" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="70"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C25" s="65"/>
+      <c r="D25" s="70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -8908,41 +9650,53 @@
       <c r="B26" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="66" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" s="70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B27" s="65" t="s">
+      <c r="B27" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="68"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="66"/>
+      <c r="D27" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B28" s="65" t="s">
+      <c r="B28" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="68"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C28" s="66"/>
+      <c r="D28" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B29" s="65" t="s">
+      <c r="B29" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="68"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C29" s="66"/>
+      <c r="D29" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -8950,9 +9704,12 @@
       <c r="B30" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="68"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C30" s="66"/>
+      <c r="D30" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -8960,9 +9717,12 @@
       <c r="B31" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="68"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C31" s="66"/>
+      <c r="D31" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -8970,9 +9730,12 @@
       <c r="B32" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="68"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C32" s="66"/>
+      <c r="D32" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -8980,59 +9743,74 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="68"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C33" s="66"/>
+      <c r="D33" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B34" s="64" t="s">
+      <c r="B34" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="70" t="s">
+      <c r="C34" s="65" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D34" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B35" s="64" t="s">
+      <c r="B35" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="70"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C35" s="65"/>
+      <c r="D35" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B36" s="64" t="s">
+      <c r="B36" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="70"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C36" s="65"/>
+      <c r="D36" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B37" s="64" t="s">
+      <c r="B37" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="C37" s="70"/>
-    </row>
-    <row r="38" spans="1:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="62" t="s">
+      <c r="C37" s="65"/>
+      <c r="D37" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="A38" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="62"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="64"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39">
         <f>A37+1</f>
         <v>24</v>
@@ -9040,11 +9818,14 @@
       <c r="B39" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="66" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D39" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -9052,9 +9833,12 @@
       <c r="B40" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="68"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C40" s="66"/>
+      <c r="D40" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -9062,9 +9846,12 @@
       <c r="B41" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="68"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C41" s="66"/>
+      <c r="D41" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -9072,9 +9859,12 @@
       <c r="B42" t="s">
         <v>44</v>
       </c>
-      <c r="C42" s="68"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C42" s="66"/>
+      <c r="D42" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -9082,9 +9872,12 @@
       <c r="B43" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="68"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C43" s="66"/>
+      <c r="D43" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -9092,9 +9885,12 @@
       <c r="B44" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="68"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C44" s="66"/>
+      <c r="D44" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -9102,190 +9898,244 @@
       <c r="B45" t="s">
         <v>120</v>
       </c>
-      <c r="C45" s="68"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="66"/>
+      <c r="D45" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B46" s="64" t="s">
+      <c r="B46" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="C46" s="69" t="s">
+      <c r="C46" s="67" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D46" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B47" s="64" t="s">
+      <c r="B47" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="C47" s="69"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C47" s="67"/>
+      <c r="D47" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B48" s="64" t="s">
+      <c r="B48" s="62" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="69"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C48" s="67"/>
+      <c r="D48" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B49" s="64" t="s">
+      <c r="B49" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="69"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="67"/>
+      <c r="D49" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B50" s="65" t="s">
+      <c r="B50" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="67" t="s">
+      <c r="C50" s="68" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B51" s="65" t="s">
+      <c r="B51" t="s">
         <v>111</v>
       </c>
-      <c r="C51" s="67"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C51" s="68"/>
+      <c r="D51" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B52" s="65" t="s">
+      <c r="B52" t="s">
         <v>122</v>
       </c>
-      <c r="C52" s="67"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C52" s="68"/>
+      <c r="D52" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B53" s="64" t="str">
+      <c r="B53" s="62" t="str">
         <f>[1]Report!$A$207</f>
         <v>Homework "Literature"</v>
       </c>
-      <c r="C53" s="69" t="s">
+      <c r="C53" s="67" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B54" s="64" t="s">
+      <c r="B54" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="C54" s="69"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C54" s="67"/>
+      <c r="D54" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B55" s="64" t="s">
+      <c r="B55" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="69"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C55" s="67"/>
+      <c r="D55" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B56" s="65" t="s">
+      <c r="B56" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="67" t="s">
+      <c r="C56" s="68" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B57" s="65" t="s">
+      <c r="B57" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="67"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C57" s="68"/>
+      <c r="D57" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58">
         <f>A57+1</f>
         <v>43</v>
       </c>
-      <c r="B58" s="65" t="s">
+      <c r="B58" t="s">
         <v>113</v>
       </c>
-      <c r="C58" s="67"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C58" s="68"/>
+      <c r="D58" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B59" s="65" t="s">
+      <c r="B59" t="s">
         <v>114</v>
       </c>
-      <c r="C59" s="67"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C59" s="68"/>
+      <c r="D59" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B60" s="64" t="s">
+      <c r="B60" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="69" t="s">
+      <c r="C60" s="67" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B61" s="64" t="s">
+      <c r="B61" s="62" t="s">
         <v>119</v>
       </c>
-      <c r="C61" s="69"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C61" s="67"/>
+      <c r="D61" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B62" s="64" t="s">
+      <c r="B62" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="C62" s="69"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C62" s="67"/>
+      <c r="D62" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -9293,39 +10143,48 @@
       <c r="B63" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="67" t="s">
+      <c r="C63" s="68" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B64" s="66" t="s">
+      <c r="B64" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="C64" s="67"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C64" s="68"/>
+      <c r="D64" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B65" s="66" t="s">
+      <c r="B65" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="C65" s="67"/>
-    </row>
-    <row r="66" spans="1:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="A66" s="62" t="s">
+      <c r="C65" s="68"/>
+      <c r="D65" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="A66" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B66" s="62"/>
-      <c r="C66" s="62"/>
-      <c r="D66" s="62"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B66" s="64"/>
+      <c r="C66" s="64"/>
+      <c r="D66" s="64"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67">
         <f>A65+1</f>
         <v>51</v>
@@ -9333,8 +10192,11 @@
       <c r="B67" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D67" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -9342,8 +10204,11 @@
       <c r="B68" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D68" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -9351,8 +10216,11 @@
       <c r="B69" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D69" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -9360,8 +10228,11 @@
       <c r="B70" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D70" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71">
         <f>A70+1</f>
         <v>55</v>
@@ -9369,8 +10240,11 @@
       <c r="B71" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D71" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -9378,8 +10252,11 @@
       <c r="B72" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D72" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -9387,8 +10264,11 @@
       <c r="B73" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D73" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -9396,29 +10276,49 @@
       <c r="B74" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D74" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D75" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D76" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D77" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78">
         <f t="shared" si="0"/>
         <v>62</v>
+      </c>
+      <c r="D78" s="70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D79" s="70" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9443,11 +10343,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -9464,7 +10364,7 @@
       <c r="P1" s="11"/>
       <c r="Q1" s="11"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
@@ -9481,7 +10381,7 @@
       <c r="P2" s="11"/>
       <c r="Q2" s="11"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -9498,7 +10398,7 @@
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -9515,7 +10415,7 @@
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -9532,7 +10432,7 @@
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -9549,7 +10449,7 @@
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
     </row>
-    <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -9568,28 +10468,28 @@
       <c r="P7" s="12"/>
       <c r="Q7" s="11"/>
     </row>
-    <row r="8" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
       <c r="Q8" s="11"/>
     </row>
-    <row r="9" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -9608,7 +10508,7 @@
       <c r="P9" s="12"/>
       <c r="Q9" s="11"/>
     </row>
-    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -9625,7 +10525,7 @@
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
     </row>
-    <row r="11" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14" t="s">
@@ -9672,7 +10572,7 @@
       </c>
       <c r="Q11" s="11"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="18"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
@@ -9719,7 +10619,7 @@
       </c>
       <c r="Q12" s="11"/>
     </row>
-    <row r="13" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
         <v>29</v>
       </c>
@@ -9744,7 +10644,7 @@
       <c r="P13" s="28"/>
       <c r="Q13" s="11"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="29">
         <v>1</v>
       </c>
@@ -9770,7 +10670,7 @@
       <c r="Q14" s="35"/>
       <c r="R14" s="36"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="37">
         <f>A14+1</f>
         <v>2</v>
@@ -9797,7 +10697,7 @@
       <c r="Q15" s="35"/>
       <c r="R15" s="36"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="37">
         <f t="shared" ref="A16:A30" si="0">A15+1</f>
         <v>3</v>
@@ -9824,7 +10724,7 @@
       <c r="Q16" s="35"/>
       <c r="R16" s="36"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -9849,7 +10749,7 @@
       <c r="Q17" s="35"/>
       <c r="R17" s="36"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -9874,7 +10774,7 @@
       <c r="Q18" s="35"/>
       <c r="R18" s="36"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -9897,7 +10797,7 @@
       <c r="Q19" s="35"/>
       <c r="R19" s="36"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="37">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -9920,7 +10820,7 @@
       <c r="Q20" s="35"/>
       <c r="R20" s="36"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -9943,7 +10843,7 @@
       <c r="Q21" s="35"/>
       <c r="R21" s="36"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -9966,7 +10866,7 @@
       <c r="Q22" s="35"/>
       <c r="R22" s="36"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9989,7 +10889,7 @@
       <c r="Q23" s="35"/>
       <c r="R23" s="36"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -10012,7 +10912,7 @@
       <c r="Q24" s="35"/>
       <c r="R24" s="36"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="37">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -10035,7 +10935,7 @@
       <c r="Q25" s="35"/>
       <c r="R25" s="36"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="37">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -10058,7 +10958,7 @@
       <c r="Q26" s="35"/>
       <c r="R26" s="36"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -10085,7 +10985,7 @@
       <c r="Q27" s="35"/>
       <c r="R27" s="36"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -10112,7 +11012,7 @@
       <c r="Q28" s="35"/>
       <c r="R28" s="36"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -10139,7 +11039,7 @@
       <c r="Q29" s="35"/>
       <c r="R29" s="36"/>
     </row>
-    <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="43">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -10166,7 +11066,7 @@
       <c r="Q30" s="35"/>
       <c r="R30" s="36"/>
     </row>
-    <row r="31" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11"/>
       <c r="C31" s="49"/>
       <c r="D31" s="11"/>
@@ -10184,7 +11084,7 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
     </row>
-    <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="C32" s="49"/>
       <c r="D32" s="11"/>
@@ -10202,7 +11102,7 @@
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
     </row>
-    <row r="33" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A33" s="50"/>
       <c r="B33" s="51" t="s">
         <v>58</v>
@@ -10230,7 +11130,7 @@
       <c r="Q33" s="35"/>
       <c r="R33" s="36"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="37"/>
       <c r="B34" s="38" t="s">
         <v>62</v>
@@ -10256,7 +11156,7 @@
       <c r="Q34" s="35"/>
       <c r="R34" s="36"/>
     </row>
-    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="43"/>
       <c r="B35" s="44" t="s">
         <v>31</v>
@@ -10278,7 +11178,7 @@
       <c r="Q35" s="35"/>
       <c r="R35" s="36"/>
     </row>
-    <row r="36" spans="1:18" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -10295,7 +11195,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -10312,7 +11212,7 @@
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -10329,7 +11229,7 @@
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="11"/>
       <c r="B39" s="57" t="s">
         <v>65</v>
@@ -10349,7 +11249,7 @@
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="11"/>
       <c r="B40" s="57" t="s">
         <v>66</v>
@@ -10371,7 +11271,7 @@
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="11"/>
       <c r="B41" s="57"/>
       <c r="D41" s="11"/>
@@ -10389,7 +11289,7 @@
       <c r="P41" s="11"/>
       <c r="Q41" s="11"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -10406,7 +11306,7 @@
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" s="11"/>
       <c r="B43" s="57"/>
       <c r="D43" s="11"/>
@@ -10424,7 +11324,7 @@
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -10451,11 +11351,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="11"/>
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
@@ -10471,7 +11371,7 @@
       <c r="O1" s="11"/>
       <c r="P1" s="11"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="11"/>
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
@@ -10487,7 +11387,7 @@
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -10503,7 +11403,7 @@
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -10519,7 +11419,7 @@
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -10535,7 +11435,7 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -10551,7 +11451,7 @@
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -10569,27 +11469,27 @@
       <c r="O7" s="12"/>
       <c r="P7" s="12"/>
     </row>
-    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63"/>
-    </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
+    </row>
+    <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -10607,7 +11507,7 @@
       <c r="O9" s="12"/>
       <c r="P9" s="12"/>
     </row>
-    <row r="10" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -10623,7 +11523,7 @@
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14" t="s">
@@ -10669,7 +11569,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="18"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
@@ -10715,7 +11615,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
         <v>71</v>
       </c>
@@ -10739,7 +11639,7 @@
       <c r="O13" s="27"/>
       <c r="P13" s="28"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="29">
         <v>1</v>
       </c>
@@ -10763,7 +11663,7 @@
       <c r="O14" s="33"/>
       <c r="P14" s="34"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="37">
         <f>A14+1</f>
         <v>2</v>
@@ -10788,7 +11688,7 @@
       <c r="O15" s="41"/>
       <c r="P15" s="42"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="37">
         <f t="shared" ref="A16:A30" si="0">A15+1</f>
         <v>3</v>
@@ -10813,7 +11713,7 @@
       <c r="O16" s="41"/>
       <c r="P16" s="42"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -10836,7 +11736,7 @@
       <c r="O17" s="41"/>
       <c r="P17" s="42"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -10859,7 +11759,7 @@
       <c r="O18" s="41"/>
       <c r="P18" s="42"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -10880,7 +11780,7 @@
       <c r="O19" s="41"/>
       <c r="P19" s="42"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="37">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -10901,7 +11801,7 @@
       <c r="O20" s="41"/>
       <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -10922,7 +11822,7 @@
       <c r="O21" s="41"/>
       <c r="P21" s="42"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -10943,7 +11843,7 @@
       <c r="O22" s="41"/>
       <c r="P22" s="42"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -10964,7 +11864,7 @@
       <c r="O23" s="41"/>
       <c r="P23" s="42"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -10985,7 +11885,7 @@
       <c r="O24" s="41"/>
       <c r="P24" s="42"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="37">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -11006,7 +11906,7 @@
       <c r="O25" s="41"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="37">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -11027,7 +11927,7 @@
       <c r="O26" s="41"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -11052,7 +11952,7 @@
       <c r="O27" s="41"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="37">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -11077,7 +11977,7 @@
       <c r="O28" s="41"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -11102,7 +12002,7 @@
       <c r="O29" s="41"/>
       <c r="P29" s="42"/>
     </row>
-    <row r="30" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="43">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -11127,7 +12027,7 @@
       <c r="O30" s="47"/>
       <c r="P30" s="48"/>
     </row>
-    <row r="31" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11"/>
       <c r="C31" s="49"/>
       <c r="D31" s="11"/>
@@ -11144,7 +12044,7 @@
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
     </row>
-    <row r="32" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="C32" s="49"/>
       <c r="D32" s="11"/>
@@ -11161,7 +12061,7 @@
       <c r="O32" s="11"/>
       <c r="P32" s="11"/>
     </row>
-    <row r="33" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A33" s="50"/>
       <c r="B33" s="51" t="s">
         <v>79</v>
@@ -11187,7 +12087,7 @@
       <c r="O33" s="54"/>
       <c r="P33" s="55"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="37"/>
       <c r="B34" s="38" t="s">
         <v>83</v>
@@ -11211,7 +12111,7 @@
       </c>
       <c r="P34" s="42"/>
     </row>
-    <row r="35" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="43"/>
       <c r="B35" s="44" t="s">
         <v>86</v>
@@ -11231,7 +12131,7 @@
       <c r="O35" s="47"/>
       <c r="P35" s="48"/>
     </row>
-    <row r="36" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
@@ -11247,7 +12147,7 @@
       <c r="O36" s="11"/>
       <c r="P36" s="11"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
@@ -11263,7 +12163,7 @@
       <c r="O37" s="11"/>
       <c r="P37" s="11"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" s="11"/>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
@@ -11279,7 +12179,7 @@
       <c r="O38" s="11"/>
       <c r="P38" s="11"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="11"/>
       <c r="B39" s="57" t="s">
         <v>87</v>
@@ -11298,7 +12198,7 @@
       <c r="O39" s="11"/>
       <c r="P39" s="11"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
@@ -11316,7 +12216,7 @@
       <c r="O40" s="11"/>
       <c r="P40" s="11"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" s="11"/>
       <c r="B41" s="57"/>
       <c r="D41" s="11"/>
@@ -11333,7 +12233,7 @@
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
@@ -11349,7 +12249,7 @@
       <c r="O42" s="11"/>
       <c r="P42" s="11"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" s="11"/>
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
@@ -11365,7 +12265,7 @@
       <c r="O43" s="11"/>
       <c r="P43" s="11"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" s="11"/>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -11391,20 +12291,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A7:I25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -11415,7 +12315,7 @@
       </c>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>19</v>
       </c>
@@ -11427,7 +12327,7 @@
       </c>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="H12" s="8" t="s">
@@ -11435,14 +12335,14 @@
       </c>
       <c r="I12" s="9"/>
     </row>
-    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="B15" s="62" t="s">
+    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="B15" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
         <v>14</v>
       </c>
@@ -11456,7 +12356,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -11464,32 +12364,32 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>90</v>
       </c>
@@ -11502,4 +12402,10 @@
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{defa4170-0d19-0005-0004-bc88714345d2}" enabled="1" method="Standard" siteId="{4f455e02-c0f5-4dd7-8284-c56491661975}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/ProjectManagement/Checklist.xlsx
+++ b/ProjectManagement/Checklist.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBEDBD8-D37D-4A48-9B82-881FE7040B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505A4640-FEBE-C944-9CBF-3676E294B8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3800" yWindow="600" windowWidth="21800" windowHeight="14200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
@@ -1196,6 +1196,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1213,13 +1220,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9465,11 +9465,11 @@
       <c r="I6" s="9"/>
     </row>
     <row r="9" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -9491,12 +9491,12 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
@@ -9505,10 +9505,10 @@
       <c r="B15" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="70" t="b">
+      <c r="D15" s="64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9520,8 +9520,8 @@
       <c r="B16" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="65"/>
-      <c r="D16" s="70" t="b">
+      <c r="C16" s="66"/>
+      <c r="D16" s="64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9533,8 +9533,8 @@
       <c r="B17" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="65"/>
-      <c r="D17" s="70" t="b">
+      <c r="C17" s="66"/>
+      <c r="D17" s="64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9546,8 +9546,8 @@
       <c r="B18" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="70" t="b">
+      <c r="C18" s="66"/>
+      <c r="D18" s="64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9559,8 +9559,8 @@
       <c r="B19" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="65"/>
-      <c r="D19" s="70" t="b">
+      <c r="C19" s="66"/>
+      <c r="D19" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9572,8 +9572,8 @@
       <c r="B20" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="65"/>
-      <c r="D20" s="70" t="b">
+      <c r="C20" s="66"/>
+      <c r="D20" s="64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9585,8 +9585,8 @@
       <c r="B21" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="65"/>
-      <c r="D21" s="70" t="b">
+      <c r="C21" s="66"/>
+      <c r="D21" s="64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9598,8 +9598,8 @@
       <c r="B22" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="65"/>
-      <c r="D22" s="70" t="b">
+      <c r="C22" s="66"/>
+      <c r="D22" s="64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9611,8 +9611,8 @@
       <c r="B23" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="65"/>
-      <c r="D23" s="70" t="b">
+      <c r="C23" s="66"/>
+      <c r="D23" s="64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9624,8 +9624,8 @@
       <c r="B24" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="65"/>
-      <c r="D24" s="70" t="b">
+      <c r="C24" s="66"/>
+      <c r="D24" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9637,8 +9637,8 @@
       <c r="B25" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="65"/>
-      <c r="D25" s="70" t="b">
+      <c r="C25" s="66"/>
+      <c r="D25" s="64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9650,10 +9650,10 @@
       <c r="B26" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="C26" s="67" t="s">
         <v>128</v>
       </c>
-      <c r="D26" s="70" t="b">
+      <c r="D26" s="64" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9665,8 +9665,8 @@
       <c r="B27" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="66"/>
-      <c r="D27" s="70" t="b">
+      <c r="C27" s="67"/>
+      <c r="D27" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9678,8 +9678,8 @@
       <c r="B28" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="66"/>
-      <c r="D28" s="70" t="b">
+      <c r="C28" s="67"/>
+      <c r="D28" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9691,8 +9691,8 @@
       <c r="B29" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="66"/>
-      <c r="D29" s="70" t="b">
+      <c r="C29" s="67"/>
+      <c r="D29" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9704,9 +9704,9 @@
       <c r="B30" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="66"/>
-      <c r="D30" s="70" t="b">
-        <v>0</v>
+      <c r="C30" s="67"/>
+      <c r="D30" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -9717,8 +9717,8 @@
       <c r="B31" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="66"/>
-      <c r="D31" s="70" t="b">
+      <c r="C31" s="67"/>
+      <c r="D31" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9730,8 +9730,8 @@
       <c r="B32" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="66"/>
-      <c r="D32" s="70" t="b">
+      <c r="C32" s="67"/>
+      <c r="D32" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9743,8 +9743,8 @@
       <c r="B33" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="66"/>
-      <c r="D33" s="70" t="b">
+      <c r="C33" s="67"/>
+      <c r="D33" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9756,11 +9756,11 @@
       <c r="B34" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="65" t="s">
+      <c r="C34" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="D34" s="70" t="b">
-        <v>0</v>
+      <c r="D34" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -9771,9 +9771,9 @@
       <c r="B35" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="65"/>
-      <c r="D35" s="70" t="b">
-        <v>0</v>
+      <c r="C35" s="66"/>
+      <c r="D35" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -9784,8 +9784,8 @@
       <c r="B36" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="65"/>
-      <c r="D36" s="70" t="b">
+      <c r="C36" s="66"/>
+      <c r="D36" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9797,18 +9797,18 @@
       <c r="B37" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="C37" s="65"/>
-      <c r="D37" s="70" t="b">
-        <v>0</v>
+      <c r="C37" s="66"/>
+      <c r="D37" s="64" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A38" s="64" t="s">
+      <c r="A38" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="64"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
+      <c r="B38" s="65"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39">
@@ -9818,10 +9818,10 @@
       <c r="B39" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="66" t="s">
+      <c r="C39" s="67" t="s">
         <v>130</v>
       </c>
-      <c r="D39" s="70" t="b">
+      <c r="D39" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9833,8 +9833,8 @@
       <c r="B40" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="66"/>
-      <c r="D40" s="70" t="b">
+      <c r="C40" s="67"/>
+      <c r="D40" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9846,8 +9846,8 @@
       <c r="B41" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="66"/>
-      <c r="D41" s="70" t="b">
+      <c r="C41" s="67"/>
+      <c r="D41" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9859,8 +9859,8 @@
       <c r="B42" t="s">
         <v>44</v>
       </c>
-      <c r="C42" s="66"/>
-      <c r="D42" s="70" t="b">
+      <c r="C42" s="67"/>
+      <c r="D42" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9872,8 +9872,8 @@
       <c r="B43" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="66"/>
-      <c r="D43" s="70" t="b">
+      <c r="C43" s="67"/>
+      <c r="D43" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9885,8 +9885,8 @@
       <c r="B44" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="66"/>
-      <c r="D44" s="70" t="b">
+      <c r="C44" s="67"/>
+      <c r="D44" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9898,8 +9898,8 @@
       <c r="B45" t="s">
         <v>120</v>
       </c>
-      <c r="C45" s="66"/>
-      <c r="D45" s="70" t="b">
+      <c r="C45" s="67"/>
+      <c r="D45" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9911,10 +9911,10 @@
       <c r="B46" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="D46" s="70" t="b">
+      <c r="D46" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9926,8 +9926,8 @@
       <c r="B47" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="C47" s="67"/>
-      <c r="D47" s="70" t="b">
+      <c r="C47" s="68"/>
+      <c r="D47" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9939,8 +9939,8 @@
       <c r="B48" s="62" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="67"/>
-      <c r="D48" s="70" t="b">
+      <c r="C48" s="68"/>
+      <c r="D48" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9952,8 +9952,8 @@
       <c r="B49" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="67"/>
-      <c r="D49" s="70" t="b">
+      <c r="C49" s="68"/>
+      <c r="D49" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9965,10 +9965,10 @@
       <c r="B50" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="69" t="s">
         <v>132</v>
       </c>
-      <c r="D50" s="70" t="b">
+      <c r="D50" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9980,8 +9980,8 @@
       <c r="B51" t="s">
         <v>111</v>
       </c>
-      <c r="C51" s="68"/>
-      <c r="D51" s="70" t="b">
+      <c r="C51" s="69"/>
+      <c r="D51" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9993,8 +9993,8 @@
       <c r="B52" t="s">
         <v>122</v>
       </c>
-      <c r="C52" s="68"/>
-      <c r="D52" s="70" t="b">
+      <c r="C52" s="69"/>
+      <c r="D52" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10007,10 +10007,10 @@
         <f>[1]Report!$A$207</f>
         <v>Homework "Literature"</v>
       </c>
-      <c r="C53" s="67" t="s">
+      <c r="C53" s="68" t="s">
         <v>133</v>
       </c>
-      <c r="D53" s="70" t="b">
+      <c r="D53" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10022,8 +10022,8 @@
       <c r="B54" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="C54" s="67"/>
-      <c r="D54" s="70" t="b">
+      <c r="C54" s="68"/>
+      <c r="D54" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10035,8 +10035,8 @@
       <c r="B55" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="C55" s="67"/>
-      <c r="D55" s="70" t="b">
+      <c r="C55" s="68"/>
+      <c r="D55" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10048,10 +10048,10 @@
       <c r="B56" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="68" t="s">
+      <c r="C56" s="69" t="s">
         <v>134</v>
       </c>
-      <c r="D56" s="70" t="b">
+      <c r="D56" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10063,8 +10063,8 @@
       <c r="B57" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="68"/>
-      <c r="D57" s="70" t="b">
+      <c r="C57" s="69"/>
+      <c r="D57" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10076,8 +10076,8 @@
       <c r="B58" t="s">
         <v>113</v>
       </c>
-      <c r="C58" s="68"/>
-      <c r="D58" s="70" t="b">
+      <c r="C58" s="69"/>
+      <c r="D58" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10089,8 +10089,8 @@
       <c r="B59" t="s">
         <v>114</v>
       </c>
-      <c r="C59" s="68"/>
-      <c r="D59" s="70" t="b">
+      <c r="C59" s="69"/>
+      <c r="D59" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10102,10 +10102,10 @@
       <c r="B60" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="C60" s="67" t="s">
+      <c r="C60" s="68" t="s">
         <v>135</v>
       </c>
-      <c r="D60" s="70" t="b">
+      <c r="D60" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10117,8 +10117,8 @@
       <c r="B61" s="62" t="s">
         <v>119</v>
       </c>
-      <c r="C61" s="67"/>
-      <c r="D61" s="70" t="b">
+      <c r="C61" s="68"/>
+      <c r="D61" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10130,8 +10130,8 @@
       <c r="B62" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="C62" s="67"/>
-      <c r="D62" s="70" t="b">
+      <c r="C62" s="68"/>
+      <c r="D62" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10143,10 +10143,10 @@
       <c r="B63" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="68" t="s">
+      <c r="C63" s="69" t="s">
         <v>136</v>
       </c>
-      <c r="D63" s="70" t="b">
+      <c r="D63" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10158,8 +10158,8 @@
       <c r="B64" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="C64" s="68"/>
-      <c r="D64" s="70" t="b">
+      <c r="C64" s="69"/>
+      <c r="D64" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10171,18 +10171,18 @@
       <c r="B65" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="C65" s="68"/>
-      <c r="D65" s="70" t="b">
+      <c r="C65" s="69"/>
+      <c r="D65" s="64" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A66" s="64" t="s">
+      <c r="A66" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="B66" s="64"/>
-      <c r="C66" s="64"/>
-      <c r="D66" s="64"/>
+      <c r="B66" s="65"/>
+      <c r="C66" s="65"/>
+      <c r="D66" s="65"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67">
@@ -10192,7 +10192,7 @@
       <c r="B67" t="s">
         <v>36</v>
       </c>
-      <c r="D67" s="70" t="b">
+      <c r="D67" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10204,7 +10204,7 @@
       <c r="B68" t="s">
         <v>37</v>
       </c>
-      <c r="D68" s="70" t="b">
+      <c r="D68" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10216,7 +10216,7 @@
       <c r="B69" t="s">
         <v>38</v>
       </c>
-      <c r="D69" s="70" t="b">
+      <c r="D69" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10228,7 +10228,7 @@
       <c r="B70" t="s">
         <v>47</v>
       </c>
-      <c r="D70" s="70" t="b">
+      <c r="D70" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10240,7 +10240,7 @@
       <c r="B71" t="s">
         <v>43</v>
       </c>
-      <c r="D71" s="70" t="b">
+      <c r="D71" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       <c r="B72" t="s">
         <v>42</v>
       </c>
-      <c r="D72" s="70" t="b">
+      <c r="D72" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       <c r="B73" t="s">
         <v>45</v>
       </c>
-      <c r="D73" s="70" t="b">
+      <c r="D73" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10276,7 +10276,7 @@
       <c r="B74" t="s">
         <v>48</v>
       </c>
-      <c r="D74" s="70" t="b">
+      <c r="D74" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="D75" s="70" t="b">
+      <c r="D75" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="D76" s="70" t="b">
+      <c r="D76" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="D77" s="70" t="b">
+      <c r="D77" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10312,12 +10312,12 @@
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="D78" s="70" t="b">
+      <c r="D78" s="64" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D79" s="70" t="b">
+      <c r="D79" s="64" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10472,21 +10472,21 @@
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="70"/>
       <c r="Q8" s="11"/>
     </row>
     <row r="9" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -11473,21 +11473,21 @@
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="70"/>
     </row>
     <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="11"/>
@@ -12336,11 +12336,11 @@
       <c r="I12" s="9"/>
     </row>
     <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
